--- a/data/trans_camb/IP18A02-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP18A02-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,16; 10,45</t>
+          <t>-10,56; 10,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,28; 12,87</t>
+          <t>-7,87; 13,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,4; 23,23</t>
+          <t>-14,26; 24,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-19,21; 0,38</t>
+          <t>-19,71; 0,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-13,86; 8,12</t>
+          <t>-13,85; 7,49</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-22,98; 11,67</t>
+          <t>-22,84; 12,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-13,07; 1,74</t>
+          <t>-12,09; 2,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 7,93</t>
+          <t>-7,54; 6,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-12,31; 15,21</t>
+          <t>-13,7; 14,27</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-24,03; 29,27</t>
+          <t>-22,58; 28,78</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-15,31; 37,23</t>
+          <t>-16,43; 36,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-30,46; 65,14</t>
+          <t>-31,68; 65,98</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-37,08; 0,86</t>
+          <t>-37,02; 0,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-26,31; 19,6</t>
+          <t>-27,78; 18,24</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-45,76; 27,41</t>
+          <t>-45,42; 26,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-27,11; 4,11</t>
+          <t>-25,17; 5,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-15,52; 20,01</t>
+          <t>-15,35; 17,39</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-26,42; 37,35</t>
+          <t>-29,3; 34,58</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,69; 1,84</t>
+          <t>-12,09; 0,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-15,78; -3,66</t>
+          <t>-16,24; -3,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-22,86; 1,14</t>
+          <t>-22,66; 1,5</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,49; 2,77</t>
+          <t>-8,05; 4,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 5,6</t>
+          <t>-5,84; 5,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-15,08; 6,75</t>
+          <t>-15,07; 6,78</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-8,29; 0,08</t>
+          <t>-8,83; 0,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,95; -0,19</t>
+          <t>-9,42; -0,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-16,64; -0,84</t>
+          <t>-16,15; 0,1</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-39,73; 8,65</t>
+          <t>-40,01; 2,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-53,69; -15,3</t>
+          <t>-54,01; -14,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-80,0; 5,23</t>
+          <t>-81,85; 7,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-35,78; 16,66</t>
+          <t>-34,08; 20,86</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-26,88; 32,99</t>
+          <t>-25,45; 32,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-66,91; 37,17</t>
+          <t>-70,5; 37,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-32,8; 0,28</t>
+          <t>-33,38; 2,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-34,43; -0,13</t>
+          <t>-36,18; -1,98</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-66,02; -2,51</t>
+          <t>-65,87; 1,05</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,03; 2,71</t>
+          <t>-12,91; 2,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,78; 2,11</t>
+          <t>-12,49; 2,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,76; 4,56</t>
+          <t>-17,74; 5,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 5,33</t>
+          <t>-8,38; 5,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,61; 1,73</t>
+          <t>-11,43; 1,41</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,72; 11,7</t>
+          <t>-9,94; 11,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,55; 1,95</t>
+          <t>-7,94; 1,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,95; -0,12</t>
+          <t>-9,45; 0,27</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-11,61; 4,67</t>
+          <t>-11,46; 5,38</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-52,61; 23,43</t>
+          <t>-54,63; 18,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-55,04; 15,3</t>
+          <t>-52,75; 19,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-81,81; 34,81</t>
+          <t>-85,54; 36,64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-46,49; 59,77</t>
+          <t>-47,03; 51,78</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-62,16; 19,09</t>
+          <t>-63,68; 14,71</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-67,99; 105,84</t>
+          <t>-65,41; 112,03</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-44,46; 14,71</t>
+          <t>-42,76; 14,36</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-51,25; -0,78</t>
+          <t>-49,86; 2,58</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-65,01; 32,2</t>
+          <t>-62,36; 39,57</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 5,95</t>
+          <t>-5,57; 6,41</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,38; 0,66</t>
+          <t>-9,18; 0,91</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 27,97</t>
+          <t>-4,43; 24,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 7,53</t>
+          <t>-2,1; 7,9</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 9,47</t>
+          <t>-1,48; 8,72</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,57; 25,06</t>
+          <t>1,71; 25,89</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 4,95</t>
+          <t>-2,3; 5,32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 3,92</t>
+          <t>-4,04; 3,71</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,25; 19,45</t>
+          <t>2,3; 20,92</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-41,01; 82,62</t>
+          <t>-45,88; 88,64</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-70,34; 16,36</t>
+          <t>-70,92; 13,83</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-32,56; 360,91</t>
+          <t>-45,12; 295,78</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-25,97; 172,88</t>
+          <t>-27,28; 164,16</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-14,14; 209,76</t>
+          <t>-22,44; 185,35</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,19; 488,65</t>
+          <t>12,16; 470,59</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-21,28; 76,11</t>
+          <t>-23,01; 80,52</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-35,75; 55,93</t>
+          <t>-39,18; 55,49</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>19,71; 273,5</t>
+          <t>23,19; 300,72</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 1,51</t>
+          <t>-6,34; 1,68</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8,2; -0,95</t>
+          <t>-8,35; -0,78</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-10,89; 3,36</t>
+          <t>-10,55; 3,27</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 2,19</t>
+          <t>-5,35; 2,12</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 2,68</t>
+          <t>-4,39; 2,67</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,64; 5,89</t>
+          <t>-6,73; 5,55</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 0,84</t>
+          <t>-4,51; 1,12</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 0,02</t>
+          <t>-5,04; 0,19</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-6,99; 2,2</t>
+          <t>-7,02; 2,15</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-24,46; 7,67</t>
+          <t>-24,08; 8,58</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-32,55; -4,29</t>
+          <t>-32,78; -3,46</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-45,47; 14,95</t>
+          <t>-43,12; 14,82</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-21,79; 12,28</t>
+          <t>-24,57; 11,46</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-21,19; 14,48</t>
+          <t>-20,25; 14,37</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-31,71; 30,88</t>
+          <t>-31,11; 29,31</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-18,57; 3,98</t>
+          <t>-19,19; 5,45</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-21,49; 0,11</t>
+          <t>-21,51; 1,04</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-31,14; 10,65</t>
+          <t>-31,52; 10,05</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP18A02-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP18A02-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-10,56; 10,34</t>
+          <t>-11,34; 9,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 13,12</t>
+          <t>-7,11; 13,76</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-14,26; 24,76</t>
+          <t>-13,73; 24,95</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-19,71; 0,15</t>
+          <t>-20,92; 0,55</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-13,85; 7,49</t>
+          <t>-14,35; 6,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-22,84; 12,11</t>
+          <t>-22,77; 12,15</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-12,09; 2,47</t>
+          <t>-12,56; 2,06</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 6,82</t>
+          <t>-7,58; 6,7</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-13,7; 14,27</t>
+          <t>-13,83; 13,11</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-22,58; 28,78</t>
+          <t>-23,9; 26,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-16,43; 36,87</t>
+          <t>-15,27; 38,81</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-31,68; 65,98</t>
+          <t>-31,29; 64,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-37,02; 0,43</t>
+          <t>-39,24; 1,59</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-27,78; 18,24</t>
+          <t>-27,45; 17,28</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-45,42; 26,25</t>
+          <t>-45,77; 27,7</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-25,17; 5,85</t>
+          <t>-25,02; 6,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-15,35; 17,39</t>
+          <t>-16,38; 16,93</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-29,3; 34,58</t>
+          <t>-29,98; 31,21</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,09; 0,55</t>
+          <t>-11,93; 0,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-16,24; -3,28</t>
+          <t>-15,51; -2,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-22,66; 1,5</t>
+          <t>-23,27; 1,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,05; 4,04</t>
+          <t>-8,19; 3,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 5,86</t>
+          <t>-6,29; 5,19</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-15,07; 6,78</t>
+          <t>-14,21; 7,76</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-8,83; 0,29</t>
+          <t>-8,69; -0,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,42; -0,48</t>
+          <t>-8,84; -0,45</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-16,15; 0,1</t>
+          <t>-16,39; -0,51</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-40,01; 2,41</t>
+          <t>-40,47; 2,4</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-54,01; -14,37</t>
+          <t>-52,35; -10,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-81,85; 7,59</t>
+          <t>-82,83; 6,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-34,08; 20,86</t>
+          <t>-33,94; 18,89</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-25,45; 32,98</t>
+          <t>-26,3; 28,96</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-70,5; 37,9</t>
+          <t>-65,83; 40,85</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-33,38; 2,14</t>
+          <t>-33,54; 0,02</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-36,18; -1,98</t>
+          <t>-35,17; -1,96</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-65,87; 1,05</t>
+          <t>-65,07; -1,33</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,91; 2,42</t>
+          <t>-12,94; 2,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,49; 2,39</t>
+          <t>-13,17; 1,57</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,74; 5,46</t>
+          <t>-16,73; 7,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,38; 5,47</t>
+          <t>-8,16; 5,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 1,41</t>
+          <t>-10,8; 1,74</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-9,94; 11,49</t>
+          <t>-10,15; 12,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,94; 1,9</t>
+          <t>-7,93; 1,8</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,45; 0,27</t>
+          <t>-9,74; 0,19</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-11,46; 5,38</t>
+          <t>-11,49; 5,45</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-54,63; 18,0</t>
+          <t>-54,72; 18,28</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-52,75; 19,46</t>
+          <t>-55,63; 12,29</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-85,54; 36,64</t>
+          <t>-78,34; 49,91</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-47,03; 51,78</t>
+          <t>-47,41; 50,41</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-63,68; 14,71</t>
+          <t>-60,17; 25,6</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-65,41; 112,03</t>
+          <t>-65,59; 126,16</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-42,76; 14,36</t>
+          <t>-42,15; 13,16</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-49,86; 2,58</t>
+          <t>-49,66; 2,04</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-62,36; 39,57</t>
+          <t>-64,78; 35,84</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 6,41</t>
+          <t>-4,9; 5,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,18; 0,91</t>
+          <t>-9,07; 0,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,43; 24,25</t>
+          <t>-4,74; 27,04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 7,9</t>
+          <t>-2,27; 7,74</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 8,72</t>
+          <t>-1,36; 9,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,71; 25,89</t>
+          <t>1,69; 26,57</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 5,32</t>
+          <t>-2,18; 5,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 3,71</t>
+          <t>-3,59; 3,61</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,3; 20,92</t>
+          <t>1,38; 19,29</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-45,88; 88,64</t>
+          <t>-39,7; 77,48</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-70,92; 13,83</t>
+          <t>-71,16; 14,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-45,12; 295,78</t>
+          <t>-42,32; 319,27</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-27,28; 164,16</t>
+          <t>-27,64; 160,06</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-22,44; 185,35</t>
+          <t>-22,27; 191,8</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,16; 470,59</t>
+          <t>14,5; 506,47</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-23,01; 80,52</t>
+          <t>-23,45; 79,94</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-39,18; 55,49</t>
+          <t>-36,0; 56,17</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>23,19; 300,72</t>
+          <t>10,63; 272,65</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 1,68</t>
+          <t>-6,25; 1,58</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-8,35; -0,78</t>
+          <t>-7,93; 0,02</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-10,55; 3,27</t>
+          <t>-10,27; 3,55</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,35; 2,12</t>
+          <t>-4,87; 2,36</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 2,67</t>
+          <t>-4,45; 2,75</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 5,55</t>
+          <t>-6,78; 5,75</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 1,12</t>
+          <t>-4,4; 0,52</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 0,19</t>
+          <t>-4,85; 0,34</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 2,15</t>
+          <t>-7,78; 1,91</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-24,08; 8,58</t>
+          <t>-25,09; 7,44</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-32,78; -3,46</t>
+          <t>-31,69; -0,26</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-43,12; 14,82</t>
+          <t>-42,69; 15,6</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-24,57; 11,46</t>
+          <t>-22,08; 12,6</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-20,25; 14,37</t>
+          <t>-20,22; 14,85</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-31,11; 29,31</t>
+          <t>-31,79; 30,46</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-19,19; 5,45</t>
+          <t>-19,19; 2,61</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-21,51; 1,04</t>
+          <t>-20,92; 1,99</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-31,52; 10,05</t>
+          <t>-35,08; 9,53</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP18A02-Edad-trans_camb.xlsx
+++ b/data/trans_camb/IP18A02-Edad-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que su última consulta al médico fue por control de salud periódico</t>
+          <t>Menores cuya última consulta médica fue por control de salud periódico</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-9,61</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-3,59</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-4,94</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-0,86</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>3,12</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>4,98</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-9,61</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-3,59</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-5,65</t>
+          <t>6,5</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,56</t>
+          <t>0,67</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-11,34; 9,21</t>
+          <t>-19,21; 0,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 13,76</t>
+          <t>-13,86; 8,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,73; 24,95</t>
+          <t>-22,28; 12,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-20,92; 0,55</t>
+          <t>-11,16; 10,45</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,35; 6,85</t>
+          <t>-7,28; 12,87</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-22,77; 12,15</t>
+          <t>-12,7; 25,87</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-12,56; 2,06</t>
+          <t>-13,07; 1,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,58; 6,7</t>
+          <t>-7,45; 7,93</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-13,83; 13,11</t>
+          <t>-11,57; 16,51</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-20,23%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-7,57%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-10,39%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-2,08%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>7,52%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>12,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-20,23%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-7,57%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-11,88%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-1,26%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-23,9; 26,59</t>
+          <t>-37,08; 0,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-15,27; 38,81</t>
+          <t>-26,31; 19,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-31,29; 64,09</t>
+          <t>-44,54; 28,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-39,24; 1,59</t>
+          <t>-24,03; 29,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-27,45; 17,28</t>
+          <t>-15,31; 37,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-45,77; 27,7</t>
+          <t>-28,67; 70,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-25,02; 6,23</t>
+          <t>-27,11; 4,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-16,38; 16,93</t>
+          <t>-15,52; 20,01</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-29,98; 31,21</t>
+          <t>-23,7; 39,59</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-2,48</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,27</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-5,49</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-5,59</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-9,48</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-13,87</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-2,48</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-0,27</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-5,65</t>
+          <t>-12,65</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-9,65</t>
+          <t>-9,02</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,93; 0,48</t>
+          <t>-8,49; 2,77</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-15,51; -2,42</t>
+          <t>-6,41; 5,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-23,27; 1,13</t>
+          <t>-14,86; 8,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 3,26</t>
+          <t>-11,69; 1,84</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 5,19</t>
+          <t>-15,78; -3,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-14,21; 7,76</t>
+          <t>-21,9; 2,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-8,69; -0,06</t>
+          <t>-8,29; 0,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,84; -0,45</t>
+          <t>-8,95; -0,19</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-16,39; -0,51</t>
+          <t>-16,2; 0,27</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-12,02%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-1,3%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-26,62%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-21,02%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-35,65%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-52,18%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-12,02%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-1,3%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-27,41%</t>
+          <t>-47,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-40,9%</t>
+          <t>-38,22%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-40,47; 2,4</t>
+          <t>-35,78; 16,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-52,35; -10,18</t>
+          <t>-26,88; 32,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-82,83; 6,21</t>
+          <t>-67,5; 44,51</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-33,94; 18,89</t>
+          <t>-39,73; 8,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-26,3; 28,96</t>
+          <t>-53,69; -15,3</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-65,83; 40,85</t>
+          <t>-77,6; 13,72</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-33,54; 0,02</t>
+          <t>-32,8; 0,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-35,17; -1,96</t>
+          <t>-34,43; -0,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-65,07; -1,33</t>
+          <t>-64,76; 5,2</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-1,3</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-4,42</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-0,48</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-4,99</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-5,09</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-7,48</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-1,3</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-4,42</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-1,37</t>
+          <t>-6,32</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-4,27</t>
+          <t>-3,26</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-12,94; 2,37</t>
+          <t>-7,86; 5,33</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-13,17; 1,57</t>
+          <t>-10,61; 1,73</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-16,73; 7,09</t>
+          <t>-10,31; 13,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 5,09</t>
+          <t>-12,03; 2,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,8; 1,74</t>
+          <t>-12,78; 2,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,15; 12,17</t>
+          <t>-16,7; 7,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,93; 1,8</t>
+          <t>-8,55; 1,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-9,74; 0,19</t>
+          <t>-9,95; -0,12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-11,49; 5,45</t>
+          <t>-10,92; 6,1</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-9,42%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-32,09%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-3,5%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-26,48%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-27,0%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-39,67%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-9,42%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-32,09%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-9,97%</t>
+          <t>-33,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-26,38%</t>
+          <t>-20,09%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-54,72; 18,28</t>
+          <t>-46,49; 59,77</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-55,63; 12,29</t>
+          <t>-62,16; 19,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-78,34; 49,91</t>
+          <t>-68,02; 122,53</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-47,41; 50,41</t>
+          <t>-52,61; 23,43</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-60,17; 25,6</t>
+          <t>-55,04; 15,3</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-65,59; 126,16</t>
+          <t>-79,63; 48,84</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-42,15; 13,16</t>
+          <t>-44,46; 14,71</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-49,66; 2,04</t>
+          <t>-51,25; -0,78</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-64,78; 35,84</t>
+          <t>-61,77; 42,48</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2,62</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3,7</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>12,16</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>0,24</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-4,13</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>8,39</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2,62</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>3,7</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11,31</t>
+          <t>9,71</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>9,85</t>
+          <t>10,89</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,9; 5,57</t>
+          <t>-2,22; 7,53</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 0,68</t>
+          <t>-1,16; 9,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 27,04</t>
+          <t>2,84; 26,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 7,74</t>
+          <t>-5,14; 5,95</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 9,23</t>
+          <t>-9,38; 0,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,69; 26,57</t>
+          <t>-3,16; 29,92</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 5,52</t>
+          <t>-2,09; 4,95</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-3,59; 3,61</t>
+          <t>-3,63; 3,92</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,38; 19,29</t>
+          <t>2,8; 20,94</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>38,69%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>54,57%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>179,36%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>2,42%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-41,29%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>83,89%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>38,69%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>54,57%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>166,84%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>118,03%</t>
+          <t>130,37%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-39,7; 77,48</t>
+          <t>-25,97; 172,88</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-71,16; 14,04</t>
+          <t>-14,14; 209,76</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-42,32; 319,27</t>
+          <t>25,58; 513,98</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-27,64; 160,06</t>
+          <t>-41,01; 82,62</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-22,27; 191,8</t>
+          <t>-70,34; 16,36</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,5; 506,47</t>
+          <t>-28,59; 392,83</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-23,45; 79,94</t>
+          <t>-21,28; 76,11</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-36,0; 56,17</t>
+          <t>-35,75; 55,93</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10,63; 272,65</t>
+          <t>26,11; 296,26</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-1,38</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,72</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-0,92</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>-2,26</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>-4,31</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>-4,18</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-1,38</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-0,72</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-1,25</t>
+          <t>-2,93</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-2,69</t>
+          <t>-1,96</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 1,58</t>
+          <t>-4,79; 2,19</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,93; 0,02</t>
+          <t>-4,79; 2,68</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-10,27; 3,55</t>
+          <t>-6,58; 6,74</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 2,36</t>
+          <t>-6,21; 1,51</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 2,75</t>
+          <t>-8,2; -0,95</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 5,75</t>
+          <t>-9,88; 5,4</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 0,52</t>
+          <t>-4,18; 0,84</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,85; 0,34</t>
+          <t>-4,95; 0,02</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 1,91</t>
+          <t>-6,5; 3,16</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-6,78%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-3,56%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-4,55%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>-9,7%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>-18,44%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>-17,91%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-6,78%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-3,56%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-6,17%</t>
+          <t>-12,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-12,37%</t>
+          <t>-9,0%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-25,09; 7,44</t>
+          <t>-21,79; 12,28</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-31,69; -0,26</t>
+          <t>-21,19; 14,48</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-42,69; 15,6</t>
+          <t>-31,55; 34,01</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-22,08; 12,6</t>
+          <t>-24,46; 7,67</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-20,22; 14,85</t>
+          <t>-32,55; -4,29</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-31,79; 30,46</t>
+          <t>-41,72; 24,5</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-19,19; 2,61</t>
+          <t>-18,57; 3,98</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-20,92; 1,99</t>
+          <t>-21,49; 0,11</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-35,08; 9,53</t>
+          <t>-28,89; 15,63</t>
         </is>
       </c>
     </row>
